--- a/moving-leads/04-lead-tracker/leads.xlsx
+++ b/moving-leads/04-lead-tracker/leads.xlsx
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
